--- a/TEC and 4C/TEC files/TEC_report_latest.xlsx
+++ b/TEC and 4C/TEC files/TEC_report_latest.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -456,13 +456,681 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>Detailed Change Records:</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Change Type</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Change Details</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Customer Name</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Connection Site</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MW Connected</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>MW Increase / Decrease</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Cumulative Total Capacity (MW)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>MW Effective From</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Project Status</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Agreement Type</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>HOST TO</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Plant Type</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Project ID</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Project Number</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>New entry in TEC register.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Celtic 2 Offshore Wind Farm</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RWE Offshore Wind</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Alverdiscott 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2031-10-31</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Wind Offshore</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>a0l4L0000005ia5QAA</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>PRO-002007</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Connection Date: '2031-10-31' -&gt; '2036-12-06'</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Gwynt Glas Offshore Wind Farm</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>GWYNT GLAS OFFSHORE WIND FARM LIMITED</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Alverdiscott 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2036-12-06</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Wind Offshore</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>a0l4L0000005iiyQAA</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>PRO-001772</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Connection Date: '2033-10-31' -&gt; '2033-10-30'</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Havbredey</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HAVBREDEY LIMITED</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>New Dounreay 400kV substation</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2033-10-30</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>SHET</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Wind Offshore</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>a0l4L0000005iNUQAY</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>PRO-001628</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Connection Date: '2037-10-30' -&gt; '2037-07-30'</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Isle of Man Offshore Wind Farm</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mooir Vannin Offshore Wind Farm Limited</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>IMW01 OFFSHORE 275/66KV OFFSHORE SUBSTATION</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1320.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1320.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2037-07-30</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Wind Offshore</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>a0l8e000000ex1KAAQ</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>PRO-003698</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Gate Status: '' -&gt; '1'</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Llywelyn Extension Offshore Wind Farm</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Renantis UK Limited</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LLYWELYN EXTENSION OFFSHORE WIND FARM 66/275KV OFFSHORE SUBSTATION</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2036-12-06</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Wind Offshore</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>a0l4L0000005iySQAQ</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>PRO-002406</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Connection Date: '2028-11-01' -&gt; '2031-10-30'</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Merlin Offshore Wind Farm</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>OFFSHORE WIND LIMITED</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Alverdiscott 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2031-10-30</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Wind Offshore</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>a0l4L0000005ihVQAQ</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>PRO-001728</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Connection Date: '2029-03-31' -&gt; '2036-12-06'</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Petroc Offshore Wind Farm</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BLUEFLOAT ENERGY UK HOLDINGS LIMITED</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Alverdiscott 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2036-12-06</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Wind Offshore</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>a0l4L0000005j1UQAQ</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>PRO-001661</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -477,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,7 +1167,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -509,7 +1177,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -519,7 +1187,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -629,17 +1297,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Strathy Wood Wind Farm</t>
+          <t>Bulls Lodge Farm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RWE Renewables UK Onshore Wind Limited</t>
+          <t>548 UK INVESTMENT HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Strathy Wood 132/33kV Substation</t>
+          <t>Braintree 400kV Substation</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -650,22 +1318,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2029-12-31</t>
+          <t>2033-04-30</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Consents Approved</t>
+          <t>Scoping</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -675,61 +1343,57 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>SHET</t>
+          <t>NGET</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Wind Onshore</t>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>a0l4L0000005ionQAA</t>
+          <t>a0l8e0000010wYOAAY</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>PRO-000154</t>
+          <t>PRO-002676</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DELETED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Entry removed from TEC register.</t>
+          <t>New entry in TEC register.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Strathy Wood Wind Farm</t>
+          <t>Bulls Lodge Farm 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RWE Renewables UK Onshore Wind Limited</t>
+          <t>548 UK INVESTMENT HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Strathy Wood 132/33kV Substation</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
+          <t>Braintree 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -737,22 +1401,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2033-03-30</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Consents Approved</t>
+          <t>Scoping</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -762,57 +1426,57 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>SHET</t>
+          <t>NGET</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Wind Onshore</t>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>a0l4L0000005ionQAA</t>
+          <t>a0l8e0000010wdkAAA</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>PRO-000154-1</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+          <t>PRO-002737</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DELETED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Entry removed from TEC register.</t>
+          <t>New entry in TEC register.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Strathy Wood Wind Farm</t>
+          <t>Elmya Gissing BESS &amp; PV</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RWE Renewables UK Onshore Wind Limited</t>
+          <t>RPC ELMYA CARNATION GISSING LIMITED</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Strathy Wood 132/33kV Substation</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
+          <t>North Anglia Connection Node A 400kV</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -820,22 +1484,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>900.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>900.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2034-10-31</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Consents Approved</t>
+          <t>Scoping</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -845,57 +1509,57 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>SHET</t>
+          <t>NGET</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Wind Onshore</t>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>a0l4L0000005ionQAA</t>
+          <t>a0l8e0000012jJxAAI</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>PRO-000154-2</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+          <t>PRO-004657</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MODIFIED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Connection Date: '2028-10-30' -&gt; '2029-10-30'</t>
+          <t>New entry in TEC register.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cilfynydd Green Energy Centre</t>
+          <t>Elmya Kilworth BESS &amp; PV</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CILFYNYDD NG LIMITED</t>
+          <t>RPC ELMYA CARNATION KILWORTH LIMITED</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cilfynydd 400kV Substation</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Derbyshire Connection Node H 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -903,22 +1567,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>400.0</t>
+          <t>850.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>400.0</t>
+          <t>850.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2029-10-30</t>
+          <t>2037-10-30</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Awaiting Consents</t>
+          <t>Scoping</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -933,17 +1597,17 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Demand;Energy Storage System;PV Array (Photo Voltaic/solar);Wind Onshore</t>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>a0l4L0000005idMQAQ</t>
+          <t>a0l8e0000012khrAAA</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PRO-001663-1</t>
+          <t>PRO-004739</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -955,27 +1619,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MODIFIED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Connection Date: '2026-10-31' -&gt; '2029-07-30'</t>
+          <t>New entry in TEC register.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fleet (Tertiary)</t>
+          <t>Elmya Morningside BESS &amp; PV</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CSE23 LIMITED</t>
+          <t>ELMYA RPC UK MORNINGSIDE LIMITED</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fleet 400kV Substation</t>
+          <t>Elmya Morningside 400kV Substation</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -986,22 +1650,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2029-07-30</t>
+          <t>2033-10-31</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Consents Approved</t>
+          <t>Scoping</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1011,50 +1675,54 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>NGET</t>
+          <t>SPT</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>PV Array (Photo Voltaic/solar)</t>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>a0l4L0000005izAQAQ</t>
+          <t>a0l8e0000012fGMAAY</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>PRO-001087</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+          <t>PRO-004396</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MODIFIED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gate Status: '' -&gt; '1'</t>
+          <t>New entry in TEC register.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Halbeath</t>
+          <t>Enderby Farm</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HALBEATH SOLAR LTD</t>
+          <t>548 UK INVESTMENT HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Halbeath 132kV Substation</t>
+          <t>Earl Shilton 400kV Substation</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1065,17 +1733,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2029-07-31</t>
+          <t>2034-10-31</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1090,22 +1758,22 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>NGET</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Demand;Energy Storage System;PV Array (Photo Voltaic/solar);Reactive Compensation</t>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>a0l4L0000005ivDQAQ</t>
+          <t>a0l8e0000010wYsAAI</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PRO-002266</t>
+          <t>PRO-002682</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1117,87 +1785,6233 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>New entry in TEC register.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Enderby Farm 2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>548 UK INVESTMENT HOLDINGS LIMITED</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Earl Shilton 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2034-10-31</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>a0l8e0000010weEAAQ</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>PRO-002743</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>New entry in TEC register.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Marston Farm 2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>548 UK INVESTMENT HOLDINGS LIMITED</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Marston Vale 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>350.0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>350.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2032-10-31</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>a0l8e0000010wdzAAA</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>PRO-002740</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>New entry in TEC register.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Patford Bridge Farm</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>548 UK INVESTMENT HOLDINGS LIMITED</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Patford Bridge 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2033-10-31</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>a0l8e0000010wYiAAI</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>PRO-002680</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>New entry in TEC register.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Patford Bridge Farm 2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>548 UK INVESTMENT HOLDINGS LIMITED</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>New Patford Bridge 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>350.0</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>350.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2033-10-31</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>a0l8e0000010we4AAA</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>PRO-002741</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>New entry in TEC register.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ryhall Farm</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>548 UK INVESTMENT HOLDINGS LIMITED</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Casewick 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2034-10-31</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>a0l8e0000010wZ2AAI</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>PRO-002684</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>New entry in TEC register.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sundon Farm</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>548 UK INVESTMENT HOLDINGS LIMITED</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Dunstable 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2032-10-29</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>a0l8e0000010wZ7AAI</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>PRO-002685</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>New entry in TEC register.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sundon Farm 2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>548 UK INVESTMENT HOLDINGS LIMITED</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Dunstable 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2032-10-29</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>a0l8e0000010weTAAQ</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>PRO-002746</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>New entry in TEC register.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Yaxley Farm</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>548 UK INVESTMENT HOLDINGS LIMITED</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Yaxley 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2032-10-31</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>a0l8e0000010wZMAAY</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>PRO-002688</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>MODIFIED</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Gate Status: '' -&gt; '2'</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Iron Acton</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>IRON ACTON GREEN LIMITED</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>132kV bay at Iron Acton Substation</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>20.6</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>120.0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Connection Date: '2031-05-30' -&gt; '2031-05-31'</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Airds Hill Wind Farm</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ONPATH ENERGY LIMITED</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Airds Hill WindFarm 132kV Substation</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2031-05-31</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Energy Storage System;Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>a0l8e0000011ymbAAA</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>PRO-003545</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Connection Date: '2034-10-31' -&gt; '2037-10-31'</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Astwood  Solar Farm GEC</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ASTWOOD GREEN ENERGY LTD</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>West Anglia Connection Node G 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>520.0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>520.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2037-10-31</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>a0lJ9000000blKHIAY</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>PRO-004799</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Connection Date: '2031-10-31' -&gt; '2037-10-31'</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Beinn Dearg</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>GALILEO 19 LIMITED</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NEW TAYNUILT 132 KV SUBSTATION</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>290.0</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>290.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2037-10-31</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>SHET</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar);Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>a0lJ9000000PM5NIAW</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>PRO-005936</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Connection Date: '2034-10-31' -&gt; '2034-10-30'</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Bicker Fen</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>IB VOGT UK LTD</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Trent Valley South Connection Node C 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2034-10-30</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>a0l8e000001HxlxAAC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>PRO-004295</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Connection Date: '2033-10-31' -&gt; '2037-10-30'</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Bradford Solar Farm</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SolarFour Ltd</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Staffordshire Connection Node A 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>960.0</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>960.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2037-10-30</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>a0l8e0000011yCAAAY</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>PRO-003511</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Connection Date: '2033-10-30' -&gt; '2032-06-01'</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Bramford GEC (Ethos Green)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BRAMFORD GREEN ENERGY CENTRE LTD</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Bramford B 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>650.0</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>650.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2032-06-01</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Awaiting Consents</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>a0l8e000000f8NgAAI</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>PRO-004027</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Connection Date: '2037-03-10' -&gt; '2037-05-10'</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Caegarw Farm</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Downing Renewable Developments LLP</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Margam B 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>350.0</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>350.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2037-05-10</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>a0l8e0000010wRwAAI</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>PRO-002605</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Connection Date: '2033-09-30' -&gt; '2033-09-14'</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Capenhurst</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ENSO GREEN HOLDINGS Q LIMITED</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Capenhurst 275kV Substation</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2033-09-14</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>a0l4L0000005ioiQAA</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>PRO-000540</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Connection Date: '2029-10-30' -&gt; '2027-10-31'</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Capenhurst Tertiary</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ENSO GREEN HOLDINGS Q LIMITED</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Capenhurst 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2027-10-31</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>a0l4L0000005ikTQAQ</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>PRO-002162</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Connection Date: '2031-10-31' -&gt; '2030-10-31'</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ceislein Wind Farm</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RWE Renewables UK Onshore Wind Limited</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ceislien Wind Farm</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2030-10-31</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>SHET</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>a0l8e000000TPK3AAO</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>PRO-003256</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Connection Date: '2033-10-31' -&gt; '2031-10-31'</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Cellarhead</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ENSO GREEN HOLDINGS X LIMITED</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Cellarhead 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2031-10-31</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>a0l4L0000005ikWQAQ</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>PRO-002161</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Connection Date: '2033-10-31' -&gt; '2037-10-31'</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Chalmerston Windfarm</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BROCKWELL ENERGY LIMITED</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>CHALMERSTON WINDFARM 132kV SUBSTATION</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2037-10-31</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>a0l8e000001Ho2yAAC</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>PRO-004057</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Connection Date: '2034-10-31' -&gt; '2034-10-30'</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cottam-Ryhall Solar &amp; BESS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CRH RENEWABLES LIMITED</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Trent Valley South Connection Node B 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2034-10-30</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>a0l8e000001HozEAAS</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>PRO-004100</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Connection Date: '2038-11-30' -&gt; '2038-10-01'</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Cowley Farm 2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>COWLEY 7 RENEWABLES LTD</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Cowley 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2038-10-01</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>a0l8e0000010wdpAAA</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>PRO-002738</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Connection Date: '2032-10-29' -&gt; '2031-10-31'; Gate Status: '' -&gt; '1'</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Craighead Wind Farm</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>GALILEO 02 LIMITED</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>CRAIGHEAD WIND FARM 132kV SUBSTATION</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2031-10-31</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>a0l8e0000010wlKAAQ</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>PRO-002821</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Connection Date: '2033-10-31' -&gt; '2037-10-30'; Gate Status: '' -&gt; '1'</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Daventry High Impact Green Energy Hub (HIGEH) 1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TELIS ENERGY UK LIMITED</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Derbyshire Connection Node A 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2037-10-30</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Energy Storage System;Nuclear;PV Array (Photo Voltaic/solar);Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>a0l8e000000ewvzAAA</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>PRO-003686</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Connection Date: '2033-10-30' -&gt; '2034-10-30'</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Denton Estate Solar PV and BESS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ELGIN ENERGY ES CO LIMITED</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Navenby 132kV Substation</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2034-10-30</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Embedded</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>a0l8e0000012gYuAAI</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>PRO-004417</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Connection Date: '2034-10-31' -&gt; '2031-04-01'</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Deucheran Hill 2 Wind Farm</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>RWE Renewables UK Onshore Wind Limited</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>DEUCHERAN HILL 2 132KV SUBSTATION</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2031-04-01</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>SHET</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Energy Storage System;Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>a0l8e000001HrYyAAK</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>PRO-004208</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Connection Date: '2036-11-11' -&gt; '2036-11-01'; Gate Status: '' -&gt; '1'</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dunan Hill</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PERIGUS ENERGY UK LIMITED</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Dunan Hill 400kV substation</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>249.9</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>249.9</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2036-11-01</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>SHET</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Energy Storage System;Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>a0l8e0000012gbZAAQ</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>PRO-004433</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Connection Date: '2034-10-31' -&gt; '2036-12-06'</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>East Claydon High Impact Green Energy Hub (HIGEH) 1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EAST CLAYDON STORAGE LIMITED</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>East Claydon 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2036-12-06</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Energy Storage System;Nuclear;PV Array (Photo Voltaic/solar);Reactive Compensation;Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>a0l8e0000010wW3AAI</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>PRO-002652</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Connection Date: '2033-10-30' -&gt; '2033-10-31'</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>EcoWymondley</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Econergy International Limited</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Wymondley 2 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>249.0</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>249.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2033-10-31</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Demand;Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>a0l4L0000005j9sQAA</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>PRO-002529</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Gate Status: '' -&gt; '1'</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Edinbane Windfarm</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VATTENFALL WIND POWER LTD</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Edinbane 132/33kV Substation</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>41.4</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>41.4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>SHET</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Energy Storage System;Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>a0l4L0000005ioIQAQ</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>PRO-000135-1</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Gate Status: '' -&gt; '1'</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Edinbane Windfarm</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VATTENFALL WIND POWER LTD</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Edinbane 132/33kV Substation</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>48.6</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2033-04-30</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>SHET</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Energy Storage System;Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>a0l4L0000005ioIQAQ</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>PRO-000135-2</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Connection Date: '2027-08-01' -&gt; '2028-08-31'</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Enderby Tertiary</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CLUMP FARM SOLAR LIMITED</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Enderby 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2028-08-31</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>Consents Approved</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Direct Connection</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>NGET</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>a0l4L0000005izzQAA</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>PRO-000430</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Connection Date: '2032-10-31' -&gt; '2034-10-31'</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>EPL Suffolk</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>EPL NEWCO9 LIMITED</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>North Anglia Connection Node E 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>480.0</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>480.0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2034-10-31</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>a0l4L0000005iodQAA</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>PRO-000491-2</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>a0l8e000000f5BYAAY</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>PRO-003916</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Connection Date: '2037-10-31' -&gt; '2035-10-30'</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Epworth PV &amp; BESS Station</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>IBV KELFIELD SOLAR LTD</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Trent Valley North Connection Node B 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2035-10-30</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>a0l8e000000ew2TAAQ</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>PRO-003644</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Connection Date: '2029-10-30' -&gt; '2035-10-30'</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ewerby</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Leoda Solar Farm Limited</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Navenby 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2035-10-30</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Demand;Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>a0l4L0000005iaDQAQ</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>PRO-002017</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Connection Date: '2033-10-31' -&gt; '2037-10-30'</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Feckenham PV &amp; BESS Station</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>IB VOGT UK LTD</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Feckenham 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2037-10-30</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>a0l8e000000TPHOAA4</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>PRO-003233</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Connection Date: '2037-10-31' -&gt; '2039-10-31'</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Frome Valley Energy Park</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BIOSOUTH ENERGY LIMITED</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Chickerell-Mannington 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>43.2</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>43.2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2039-10-31</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Demand;Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>a0lJ9000000Pa9MIAS</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>PRO-006617</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Connection Date: '2031-10-31' -&gt; '2031-11-30'; Gate Status: '' -&gt; '1'</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Glen Lednock</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Glen Lednock Wind Farm Limited</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Glen Lednock 132kV Substation</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2031-11-30</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>SHET</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Energy Storage System;Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>a0l8e0000012ho5AAA</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>PRO-004520</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Connection Date: '2031-10-30' -&gt; '2031-04-30'</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Glenrothes Hybrid BESS &amp; Solar PV</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TAGENERGY DEVELOPMENT UK LIMITED</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Conland Substation</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2031-04-30</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>a0l8e000000TPJUAA4</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>PRO-003252</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Connection Date: '2032-06-30' -&gt; '2032-04-30'</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Grangemouth  Hybrid BESS &amp; Solar PV</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TAGENERGY DEVELOPMENT UK LIMITED</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Letham 400/275kV substation</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2032-04-30</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>a0l8e000000TPJeAAO</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>PRO-003254</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Connection Date: '2034-10-31' -&gt; '2031-03-01'</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Greta IV (b)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Greta IV Limited</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>North Anglia Connection Node B 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2031-03-01</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>a0l8e0000012guYAAQ</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>PRO-004499</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Connection Date: '2028-10-30' -&gt; '2028-10-31'</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Hams Hall Green Energy Centre</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>HAMS HALL NG LIMITED</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Hams Hall 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2028-10-31</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Demand;Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>a0l4L0000005iirQAA</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>PRO-001765-1</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Connection Date: '2031-10-31' -&gt; '2029-11-01'; Gate Status: '' -&gt; '1'</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>High Marnham Solar Farm</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ANESCO LIMITED</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>High Marnham 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>99.9</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>99.9</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2029-11-01</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>a0l4L0000005iY7QAI</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>PRO-001845</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Connection Date: '2029-10-30' -&gt; '2032-10-30'</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ironbridge Green Energy Centre</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>IRONBRIDGE GREEN NG LIMITED</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Ironbridge 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2032-10-30</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Awaiting Consents</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>a0l4L0000005igDQAQ</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>PRO-001711</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Connection Date: '2028-10-31' -&gt; '2033-10-31'</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Keith Solar Farm</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>KEITH SOLAR PV LIMITED</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Keith Solar Farm 275kV Substation</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2033-10-31</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>SHET</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>a0l8e0000010waMAAQ</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>PRO-002699</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Connection Date: '2037-10-31' -&gt; '2037-10-30'</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Kenwick Solar</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ANESCO LIMITED</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Shrewsbury 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>430.85</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>430.85</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2037-10-30</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>a0lJ9000000PNKlIAO</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>PRO-005989</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Connection Date: '2028-10-31' -&gt; '2029-10-31'</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Kirkton Wind Farm</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Kirkton Wind Farm Limited</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Connagill 275kV Substation</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2029-10-31</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Awaiting Consents</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>SHET</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>a0l4L0000005ikRQAQ</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>PRO-001811</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Connection Date: '2034-10-31' -&gt; '2034-10-30'</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Leadenham High Impact Green Energy Hub</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>TELIS ENERGY UK LIMITED</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Trent Valley South Connection Node A 400kV</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2034-10-30</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Energy Storage System;Nuclear;PV Array (Photo Voltaic/solar);Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>a0l8e000000f40kAAA</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>PRO-003815</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Connection Date: '2033-12-31' -&gt; '2033-12-01'</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Lethen Wind Farm</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>FRED OLSEN RENEWABLES LIMITED</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Lethen Wind Farm 132/33kV Substation</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2033-12-01</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>SHET</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>a0l4L0000005ivMQAQ</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>PRO-002307</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Connection Date: '2037-10-31' -&gt; '2037-10-30'; Gate Status: '' -&gt; '1'</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Lightsource Enderby PV+BESS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Lightsource Renewable UK Development Limited</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Derbyshire Connection Node B 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2037-10-30</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>a0l8e000000f4dhAAA</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>PRO-003854</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Connection Date: '2037-10-30' -&gt; '2038-10-30'</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Lightsource Ferryside PV</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Lightsource Renewable UK Development Limited</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>South Wales West Connection Node C 400kV</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2038-10-30</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>a0l8e000000eyX9AAI</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>PRO-003761</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Connection Date: '2034-10-31' -&gt; '2034-10-30'</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Lightsource Marston Vale 240MW PV+BESS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Lightsource Renewable UK Development Limited</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Marston Vale 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2034-10-30</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>a0l8e000000f6OSAAY</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>PRO-003981</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Gate Status: '' -&gt; '1'</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Market Harborough Green Energy Hub</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>TELIS ENERGY UK LIMITED</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>West Anglia Connection Node F 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2034-10-31</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Energy Storage System;Hydro;Nuclear;PV Array (Photo Voltaic/solar);Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>a0l8e00000120NNAAY</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>PRO-003623</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Connection Date: '2034-10-30' -&gt; '2034-10-31'</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Mid Hill</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Invenergy Development UK Ltd</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Mid Hill 132kV Substation</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>228.0</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>228.0</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2034-10-31</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Energy Storage System;Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>a0lJ9000000PDlIIAW</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>PRO-005000</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Connection Date: '2037-10-31' -&gt; '2034-10-30'; Gate Status: '' -&gt; '1'</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Morton Manor PV &amp; BESS Station</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>IB VOGT UK LTD</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>High Marnham 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2034-10-30</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>a0l8e000000f41nAAA</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>PRO-003827</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Connection Date: '2037-10-31' -&gt; '2037-10-30'</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Nant Helen</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SOLAR SECURITIES LIMITED</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>South Wales West Connection Node A 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2037-10-30</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Demand;Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>a0l8e0000010wgFAAQ</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>PRO-002766</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Connection Date: '2034-10-30' -&gt; '2034-05-30'</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Navenby Farm</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CODDINGTON 10 RENEWABLES LTD</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Coddington 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2034-05-30</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>a0l8e000001HnxlAAC</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>PRO-004045</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Connection Date: '2037-10-31' -&gt; '2037-10-30'</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>New Marton Solar Farm - PVDP</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SolarFour Ltd</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Cheshire Connection Node A 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>780.0</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>780.0</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2037-10-30</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>a0l8e000001HpecAAC</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>PRO-004139</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Connection Date: '2030-10-31' -&gt; '2037-10-31'</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ninfield</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Ninfield 10 Renewables Limited</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Sussex and Romney Connection Node A 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2037-10-31</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>a0l8e000000TPQqAAO</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>PRO-003408</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Connection Date: '2034-10-31' -&gt; '2038-10-30'</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Noventum -Long Stratton</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Noventum Power Solar 8 Limited</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>North Anglia Connection Node A 400kV</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>460.0</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>460.0</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2038-10-30</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>a0l8e0000012gHLAAY</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>PRO-004405</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Connection Date: '2034-10-31' -&gt; '2033-10-30'</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Pelham 400</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ENSO GREEN HOLDINGS X LIMITED</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>West Anglia Connection Node E 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2033-10-30</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>a0lJ9000000blPqIAI</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>PRO-004867</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Connection Date: '2037-10-31' -&gt; '2037-10-30'</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Pentir Green Energy Centre</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>INNOVA RENEWABLES LIMITED</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Pentir 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>1025.0</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1025.0</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2037-10-30</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Awaiting Consents</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Demand;Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>a0l4L0000005il9QAA</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>PRO-002345</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Connection Date: '2032-10-30' -&gt; '2032-10-31'</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Rat Hall Mod App</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Kingsway Solar Farm Limited</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>South Anglia Connection Node C 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2032-10-31</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>a0l8e000000f41YAAQ</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>PRO-003824-1</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Connection Date: '2034-10-31' -&gt; '2037-10-31'</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ratcliffe on Soar</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Starlight Energy SPV 4 Limited</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Derbyshire Connection Node F 132KV</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2037-10-31</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Embedded</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>a0l8e000000TPFSAA4</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>PRO-003224</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Connection Date: '2028-10-30' -&gt; '2030-05-31'</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Rowancraig Wind Farm</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Koehler Renewable Energy UK Limited</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>ROWANCRAIG WIND FARM 33KV SUBSTATION</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2030-05-31</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>a0l4L0000005iMUQAY</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>PRO-002455</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Connection Date: '2034-10-31' -&gt; '2037-10-30'</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Rugby High Impact Green Energy Hub (HIGEH) 1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>TELIS ENERGY UK LIMITED</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Enderby 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2037-10-30</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Energy Storage System;Nuclear;PV Array (Photo Voltaic/solar);Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>a0l8e00000120NcAAI</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>PRO-003626</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Connection Date: '2025-06-30' -&gt; '2029-04-30'</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SAGE</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>SAGE NORTH SEA LIMITED</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>St Fergus Mobil 132/11kV Substation</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2029-04-30</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>SHET</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Demand;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>a0l4L0000005iybQAA</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>PRO-002119</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Connection Date: '2035-10-30' -&gt; '2032-07-31'</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Seat Hill Wind Farm</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>PERIGUS ENERGY UK LIMITED</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Seat Hill 132kV Substation</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2032-07-31</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Energy Storage System;Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>a0lJ9000000PEyBIAW</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>PRO-005850</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Connection Date: '2032-04-01' -&gt; '2032-03-30'; Gate Status: '' -&gt; '1'</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Sheirdrim Wind Farm</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>SCOTTISHPOWER RENEWABLES (UK) LIMITED</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Sheirdrim 132kV Substation</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2032-03-30</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>SHET</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>a0l4L0000005icwQAA</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>PRO-001066</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Connection Date: '2030-12-31' -&gt; '2030-12-13'; Gate Status: '' -&gt; '1'</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Tarenni</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>TARENNI ENERGY PARK LIMITED</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Rhigos 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>188.0</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>188.0</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2030-12-13</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>a0l4L0000005iNdQAI</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>PRO-001641</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Connection Date: '2033-10-31' -&gt; '2036-07-31'</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Upper Beoch Windfarm</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>BROCKWELL ENERGY LIMITED</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>New Cumnock North 132kV Substation</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2036-07-31</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>a0l8e000001HoGMAA0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>PRO-004068</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Connection Date: '2032-10-31' -&gt; '2029-10-31'</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Waltham Cross PV &amp; BESS Sub</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>EPPING ENERGY PARK LIMITED</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Waltham Cross B 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>249.9</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>249.9</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2029-10-31</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>a0lJ9000000PERuIAO</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>PRO-005801</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Connection Date: '2033-10-31' -&gt; '2035-10-30'</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>West Melton PV &amp; BESS Station</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>IBV WEST MELTON SOLAR PARK LIMITED</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Leeds North Connection Node C 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2035-10-30</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>a0l8e000001HoBfAAK</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>PRO-004061</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Connection Date: '2034-10-01' -&gt; '2034-10-31'</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Windburn Wind Farm</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>WINDBURN WIND FARM LIMITED</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Devonside 132kV Substation</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2034-10-31</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Energy Storage System;Wind Onshore</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>a0lJ9000000POgFIAW</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>PRO-006075</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MODIFIED</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Connection Date: '2032-10-31' -&gt; '2032-01-30'</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Wymondley</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ENSO GREEN HOLDINGS LIMITED</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Wymondley 400kV Substation</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2032-01-30</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Scoping</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Direct Connection</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>NGET</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Energy Storage System;PV Array (Photo Voltaic/solar)</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>a0l4L0000005iyNQAQ</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>PRO-002187</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
